--- a/Excel Files/Orders_Revenue_By_Country_And_City.xlsx
+++ b/Excel Files/Orders_Revenue_By_Country_And_City.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3d9439836fb34a33/Documents/sales-analysis-project/Excel Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3035A897-3F9A-48D6-B3A2-34F3F588A620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{3035A897-3F9A-48D6-B3A2-34F3F588A620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{962A4528-ECF4-4CC3-AF8A-32D4A7E5E527}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B41FD783-5B86-481E-BDCA-55E215833250}"/>
   </bookViews>
@@ -28,18 +28,6 @@
     <t>City</t>
   </si>
   <si>
-    <t>total_orders</t>
-  </si>
-  <si>
-    <t>total_quantity</t>
-  </si>
-  <si>
-    <t>total_revenue</t>
-  </si>
-  <si>
-    <t>avg_unit_price</t>
-  </si>
-  <si>
     <t>Australia</t>
   </si>
   <si>
@@ -371,12 +359,27 @@
   </si>
   <si>
     <t>13897</t>
+  </si>
+  <si>
+    <t>Total Orders</t>
+  </si>
+  <si>
+    <t>Total Revenue</t>
+  </si>
+  <si>
+    <t>Average Unit Price</t>
+  </si>
+  <si>
+    <t>Total Quantity of Products Sold</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
+  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -854,8 +857,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -912,6 +918,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1234,969 +1244,971 @@
   <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="D2" s="2">
+        <v>76518</v>
+      </c>
+      <c r="E2" s="1">
+        <v>82470887</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1077.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D3" s="2">
+        <v>76403</v>
+      </c>
+      <c r="E3" s="1">
+        <v>81943046</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1072.51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D2">
-        <v>76518</v>
-      </c>
-      <c r="E2">
-        <v>82470887</v>
-      </c>
-      <c r="F2">
-        <v>1077.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D4" s="2">
+        <v>77795</v>
+      </c>
+      <c r="E4" s="1">
+        <v>83830993</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1077.5899999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="D3">
-        <v>76403</v>
-      </c>
-      <c r="E3">
-        <v>81943046</v>
-      </c>
-      <c r="F3">
-        <v>1072.51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="D5" s="2">
+        <v>229842</v>
+      </c>
+      <c r="E5" s="1">
+        <v>247980340</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1078.92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C6" t="s">
         <v>12</v>
       </c>
-      <c r="D4">
-        <v>77795</v>
-      </c>
-      <c r="E4">
-        <v>83830993</v>
-      </c>
-      <c r="F4">
-        <v>1077.5899999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="D6" s="2">
+        <v>75065</v>
+      </c>
+      <c r="E6" s="1">
+        <v>80966434</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1078.6199999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D5">
-        <v>229842</v>
-      </c>
-      <c r="E5">
-        <v>247980340</v>
-      </c>
-      <c r="F5">
-        <v>1078.92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C7" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D7" s="2">
+        <v>75965</v>
+      </c>
+      <c r="E7" s="1">
+        <v>82099144</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1080.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D6">
-        <v>75065</v>
-      </c>
-      <c r="E6">
-        <v>80966434</v>
-      </c>
-      <c r="F6">
-        <v>1078.6199999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="B8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C8" t="s">
         <v>18</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D8" s="2">
+        <v>75773</v>
+      </c>
+      <c r="E8" s="1">
+        <v>82109318</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1083.6199999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D7">
-        <v>75965</v>
-      </c>
-      <c r="E7">
-        <v>82099144</v>
-      </c>
-      <c r="F7">
-        <v>1080.75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="C9" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D9" s="2">
+        <v>76392</v>
+      </c>
+      <c r="E9" s="1">
+        <v>82016990</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1073.6300000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C10" t="s">
         <v>22</v>
       </c>
-      <c r="D8">
-        <v>75773</v>
-      </c>
-      <c r="E8">
-        <v>82109318</v>
-      </c>
-      <c r="F8">
-        <v>1083.6199999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="D10" s="2">
+        <v>75614</v>
+      </c>
+      <c r="E10" s="1">
+        <v>81454887</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1077.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C11" t="s">
         <v>24</v>
       </c>
-      <c r="D9">
-        <v>76392</v>
-      </c>
-      <c r="E9">
-        <v>82016990</v>
-      </c>
-      <c r="F9">
-        <v>1073.6300000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="D11" s="2">
+        <v>153433</v>
+      </c>
+      <c r="E11" s="1">
+        <v>165159638</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1076.43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D10">
-        <v>75614</v>
-      </c>
-      <c r="E10">
-        <v>81454887</v>
-      </c>
-      <c r="F10">
-        <v>1077.25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C12" t="s">
         <v>27</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D12" s="2">
+        <v>154352</v>
+      </c>
+      <c r="E12" s="1">
+        <v>165719192</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1073.6400000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D11">
-        <v>153433</v>
-      </c>
-      <c r="E11">
-        <v>165159638</v>
-      </c>
-      <c r="F11">
-        <v>1076.43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="C13" t="s">
         <v>29</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D13" s="2">
+        <v>75950</v>
+      </c>
+      <c r="E13" s="1">
+        <v>82163422</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1081.81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C14" t="s">
         <v>31</v>
       </c>
-      <c r="D12">
-        <v>154352</v>
-      </c>
-      <c r="E12">
-        <v>165719192</v>
-      </c>
-      <c r="F12">
-        <v>1073.6400000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="D14" s="2">
+        <v>74965</v>
+      </c>
+      <c r="E14" s="1">
+        <v>80570102</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1074.77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C15" t="s">
         <v>33</v>
       </c>
-      <c r="D13">
-        <v>75950</v>
-      </c>
-      <c r="E13">
-        <v>82163422</v>
-      </c>
-      <c r="F13">
-        <v>1081.81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="D15" s="2">
+        <v>75887</v>
+      </c>
+      <c r="E15" s="1">
+        <v>81438730</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1073.1600000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C16" t="s">
         <v>35</v>
       </c>
-      <c r="D14">
-        <v>74965</v>
-      </c>
-      <c r="E14">
-        <v>80570102</v>
-      </c>
-      <c r="F14">
-        <v>1074.77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="D16" s="2">
+        <v>153191</v>
+      </c>
+      <c r="E16" s="1">
+        <v>165260050</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1078.78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C15" t="s">
+      <c r="B17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D15">
-        <v>75887</v>
-      </c>
-      <c r="E15">
-        <v>81438730</v>
-      </c>
-      <c r="F15">
-        <v>1073.1600000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C17" t="s">
         <v>38</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D17" s="2">
+        <v>150569</v>
+      </c>
+      <c r="E17" s="1">
+        <v>161972626</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1075.74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D16">
-        <v>153191</v>
-      </c>
-      <c r="E16">
-        <v>165260050</v>
-      </c>
-      <c r="F16">
-        <v>1078.78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="B18" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C18" t="s">
         <v>41</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D18" s="2">
+        <v>302785</v>
+      </c>
+      <c r="E18" s="1">
+        <v>325659768</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1075.55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D17">
-        <v>150569</v>
-      </c>
-      <c r="E17">
-        <v>161972626</v>
-      </c>
-      <c r="F17">
-        <v>1075.74</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="B19" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C19" t="s">
         <v>44</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D19" s="2">
+        <v>77532</v>
+      </c>
+      <c r="E19" s="1">
+        <v>83377075</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1075.3900000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D18">
-        <v>302785</v>
-      </c>
-      <c r="E18">
-        <v>325659768</v>
-      </c>
-      <c r="F18">
-        <v>1075.55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="C20" t="s">
         <v>46</v>
       </c>
-      <c r="B19" t="s">
+      <c r="D20" s="2">
+        <v>77385</v>
+      </c>
+      <c r="E20" s="1">
+        <v>83279374</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1076.17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C21" t="s">
         <v>48</v>
       </c>
-      <c r="D19">
-        <v>77532</v>
-      </c>
-      <c r="E19">
-        <v>83377075</v>
-      </c>
-      <c r="F19">
-        <v>1075.3900000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="D21" s="2">
+        <v>75650</v>
+      </c>
+      <c r="E21" s="1">
+        <v>82165136</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1086.1199999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C20" t="s">
+      <c r="B22" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D20">
-        <v>77385</v>
-      </c>
-      <c r="E20">
-        <v>83279374</v>
-      </c>
-      <c r="F20">
-        <v>1076.17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C22" t="s">
         <v>51</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D22" s="2">
+        <v>74864</v>
+      </c>
+      <c r="E22" s="1">
+        <v>80499460</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1075.28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D21">
-        <v>75650</v>
-      </c>
-      <c r="E21">
-        <v>82165136</v>
-      </c>
-      <c r="F21">
-        <v>1086.1199999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="C23" t="s">
         <v>53</v>
       </c>
-      <c r="B22" t="s">
+      <c r="D23" s="2">
+        <v>76762</v>
+      </c>
+      <c r="E23" s="1">
+        <v>83350748</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1085.83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C22" t="s">
+      <c r="B24" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D22">
-        <v>74864</v>
-      </c>
-      <c r="E22">
-        <v>80499460</v>
-      </c>
-      <c r="F22">
-        <v>1075.28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="C24" t="s">
         <v>56</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D24" s="2">
+        <v>77787</v>
+      </c>
+      <c r="E24" s="1">
+        <v>83576408</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1074.43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D23">
-        <v>76762</v>
-      </c>
-      <c r="E23">
-        <v>83350748</v>
-      </c>
-      <c r="F23">
-        <v>1085.83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="C25" t="s">
         <v>58</v>
       </c>
-      <c r="B24" t="s">
+      <c r="D25" s="2">
+        <v>76461</v>
+      </c>
+      <c r="E25" s="1">
+        <v>82486622</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1078.81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C26" t="s">
         <v>60</v>
       </c>
-      <c r="D24">
-        <v>77787</v>
-      </c>
-      <c r="E24">
-        <v>83576408</v>
-      </c>
-      <c r="F24">
-        <v>1074.43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="D26" s="2">
+        <v>77062</v>
+      </c>
+      <c r="E26" s="1">
+        <v>83706593</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1086.22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="2">
+        <v>229015</v>
+      </c>
+      <c r="E27" s="1">
+        <v>246179087</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1074.95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="2">
+        <v>227917</v>
+      </c>
+      <c r="E28" s="1">
+        <v>245375347</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1076.5999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="2">
+        <v>76764</v>
+      </c>
+      <c r="E29" s="1">
+        <v>82998470</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1081.22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="2">
+        <v>227828</v>
+      </c>
+      <c r="E30" s="1">
+        <v>244923010</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1075.03</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="2">
+        <v>153849</v>
+      </c>
+      <c r="E31" s="1">
+        <v>166244072</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1080.57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="2">
+        <v>74977</v>
+      </c>
+      <c r="E32" s="1">
+        <v>80737780</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1076.83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" t="s">
         <v>58</v>
       </c>
-      <c r="B25" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25">
-        <v>76461</v>
-      </c>
-      <c r="E25">
-        <v>82486622</v>
-      </c>
-      <c r="F25">
-        <v>1078.81</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26">
-        <v>77062</v>
-      </c>
-      <c r="E26">
-        <v>83706593</v>
-      </c>
-      <c r="F26">
-        <v>1086.22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27">
-        <v>229015</v>
-      </c>
-      <c r="E27">
-        <v>246179087</v>
-      </c>
-      <c r="F27">
-        <v>1074.95</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>67</v>
-      </c>
-      <c r="B28" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" t="s">
-        <v>69</v>
-      </c>
-      <c r="D28">
-        <v>227917</v>
-      </c>
-      <c r="E28">
-        <v>245375347</v>
-      </c>
-      <c r="F28">
-        <v>1076.5999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>70</v>
-      </c>
-      <c r="B29" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" t="s">
-        <v>72</v>
-      </c>
-      <c r="D29">
-        <v>76764</v>
-      </c>
-      <c r="E29">
-        <v>82998470</v>
-      </c>
-      <c r="F29">
-        <v>1081.22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" t="s">
-        <v>74</v>
-      </c>
-      <c r="D30">
-        <v>227828</v>
-      </c>
-      <c r="E30">
-        <v>244923010</v>
-      </c>
-      <c r="F30">
-        <v>1075.03</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>75</v>
-      </c>
-      <c r="B31" t="s">
-        <v>76</v>
-      </c>
-      <c r="C31" t="s">
-        <v>77</v>
-      </c>
-      <c r="D31">
-        <v>153849</v>
-      </c>
-      <c r="E31">
-        <v>166244072</v>
-      </c>
-      <c r="F31">
-        <v>1080.57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>78</v>
-      </c>
-      <c r="B32" t="s">
+      <c r="D33" s="2">
+        <v>77518</v>
+      </c>
+      <c r="E33" s="1">
+        <v>83423079</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1076.18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C32" t="s">
+      <c r="B34" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D32">
-        <v>74977</v>
-      </c>
-      <c r="E32">
-        <v>80737780</v>
-      </c>
-      <c r="F32">
-        <v>1076.83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+      <c r="C34" t="s">
         <v>81</v>
       </c>
-      <c r="B33" t="s">
+      <c r="D34" s="2">
+        <v>227858</v>
+      </c>
+      <c r="E34" s="1">
+        <v>244917957</v>
+      </c>
+      <c r="F34" s="1">
+        <v>1074.8699999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C33" t="s">
-        <v>62</v>
-      </c>
-      <c r="D33">
-        <v>77518</v>
-      </c>
-      <c r="E33">
-        <v>83423079</v>
-      </c>
-      <c r="F33">
-        <v>1076.18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+      <c r="B35" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C35" t="s">
         <v>84</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D35" s="2">
+        <v>76230</v>
+      </c>
+      <c r="E35" s="1">
+        <v>83009401</v>
+      </c>
+      <c r="F35" s="1">
+        <v>1088.93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D34">
-        <v>227858</v>
-      </c>
-      <c r="E34">
-        <v>244917957</v>
-      </c>
-      <c r="F34">
-        <v>1074.8699999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+      <c r="C36" t="s">
         <v>86</v>
       </c>
-      <c r="B35" t="s">
+      <c r="D36" s="2">
+        <v>305742</v>
+      </c>
+      <c r="E36" s="1">
+        <v>329415320</v>
+      </c>
+      <c r="F36" s="1">
+        <v>1077.43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C35" t="s">
+      <c r="B37" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D35">
-        <v>76230</v>
-      </c>
-      <c r="E35">
-        <v>83009401</v>
-      </c>
-      <c r="F35">
-        <v>1088.93</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>86</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="C37" t="s">
         <v>89</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D37" s="2">
+        <v>304861</v>
+      </c>
+      <c r="E37" s="1">
+        <v>328969720</v>
+      </c>
+      <c r="F37" s="1">
+        <v>1079.08</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D36">
-        <v>305742</v>
-      </c>
-      <c r="E36">
-        <v>329415320</v>
-      </c>
-      <c r="F36">
-        <v>1077.43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+      <c r="B38" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C38" t="s">
         <v>92</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D38" s="2">
+        <v>75602</v>
+      </c>
+      <c r="E38" s="1">
+        <v>81730747</v>
+      </c>
+      <c r="F38" s="1">
+        <v>1081.07</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D37">
-        <v>304861</v>
-      </c>
-      <c r="E37">
-        <v>328969720</v>
-      </c>
-      <c r="F37">
-        <v>1079.08</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+      <c r="C39" t="s">
         <v>94</v>
       </c>
-      <c r="B38" t="s">
+      <c r="D39" s="2">
+        <v>153098</v>
+      </c>
+      <c r="E39" s="1">
+        <v>165168324</v>
+      </c>
+      <c r="F39" s="1">
+        <v>1078.8399999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C40" t="s">
         <v>96</v>
       </c>
-      <c r="D38">
-        <v>75602</v>
-      </c>
-      <c r="E38">
-        <v>81730747</v>
-      </c>
-      <c r="F38">
-        <v>1081.07</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>94</v>
-      </c>
-      <c r="B39" t="s">
+      <c r="D40" s="2">
+        <v>75815</v>
+      </c>
+      <c r="E40" s="1">
+        <v>81352165</v>
+      </c>
+      <c r="F40" s="1">
+        <v>1073.04</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C41" t="s">
         <v>98</v>
       </c>
-      <c r="D39">
-        <v>153098</v>
-      </c>
-      <c r="E39">
-        <v>165168324</v>
-      </c>
-      <c r="F39">
-        <v>1078.8399999999999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>94</v>
-      </c>
-      <c r="B40" t="s">
+      <c r="D41" s="2">
+        <v>75449</v>
+      </c>
+      <c r="E41" s="1">
+        <v>81273226</v>
+      </c>
+      <c r="F41" s="1">
+        <v>1077.19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C42" t="s">
         <v>100</v>
       </c>
-      <c r="D40">
-        <v>75815</v>
-      </c>
-      <c r="E40">
-        <v>81352165</v>
-      </c>
-      <c r="F40">
-        <v>1073.04</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>94</v>
-      </c>
-      <c r="B41" t="s">
+      <c r="D42" s="2">
+        <v>76611</v>
+      </c>
+      <c r="E42" s="1">
+        <v>82885606</v>
+      </c>
+      <c r="F42" s="1">
+        <v>1081.9000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C43" t="s">
         <v>102</v>
       </c>
-      <c r="D41">
-        <v>75449</v>
-      </c>
-      <c r="E41">
-        <v>81273226</v>
-      </c>
-      <c r="F41">
-        <v>1077.19</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>94</v>
-      </c>
-      <c r="B42" t="s">
+      <c r="D43" s="2">
+        <v>76479</v>
+      </c>
+      <c r="E43" s="1">
+        <v>82270744</v>
+      </c>
+      <c r="F43" s="1">
+        <v>1075.73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C44" t="s">
         <v>104</v>
       </c>
-      <c r="D42">
-        <v>76611</v>
-      </c>
-      <c r="E42">
-        <v>82885606</v>
-      </c>
-      <c r="F42">
-        <v>1081.9000000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>94</v>
-      </c>
-      <c r="B43" t="s">
+      <c r="D44" s="2">
+        <v>151661</v>
+      </c>
+      <c r="E44" s="1">
+        <v>163756511</v>
+      </c>
+      <c r="F44" s="1">
+        <v>1079.75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C45" t="s">
         <v>106</v>
       </c>
-      <c r="D43">
-        <v>76479</v>
-      </c>
-      <c r="E43">
-        <v>82270744</v>
-      </c>
-      <c r="F43">
-        <v>1075.73</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>94</v>
-      </c>
-      <c r="B44" t="s">
+      <c r="D45" s="2">
+        <v>231393</v>
+      </c>
+      <c r="E45" s="1">
+        <v>249137133</v>
+      </c>
+      <c r="F45" s="1">
+        <v>1076.68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C46" t="s">
         <v>108</v>
       </c>
-      <c r="D44">
-        <v>151661</v>
-      </c>
-      <c r="E44">
-        <v>163756511</v>
-      </c>
-      <c r="F44">
-        <v>1079.75</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>94</v>
-      </c>
-      <c r="B45" t="s">
+      <c r="D46" s="2">
+        <v>75364</v>
+      </c>
+      <c r="E46" s="1">
+        <v>81160400</v>
+      </c>
+      <c r="F46" s="1">
+        <v>1076.9100000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C47" t="s">
         <v>110</v>
       </c>
-      <c r="D45">
-        <v>231393</v>
-      </c>
-      <c r="E45">
-        <v>249137133</v>
-      </c>
-      <c r="F45">
-        <v>1076.68</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>94</v>
-      </c>
-      <c r="B46" t="s">
+      <c r="D47" s="2">
+        <v>76636</v>
+      </c>
+      <c r="E47" s="1">
+        <v>82885191</v>
+      </c>
+      <c r="F47" s="1">
+        <v>1081.54</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C48" t="s">
         <v>112</v>
       </c>
-      <c r="D46">
-        <v>75364</v>
-      </c>
-      <c r="E46">
-        <v>81160400</v>
-      </c>
-      <c r="F46">
-        <v>1076.9100000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>94</v>
-      </c>
-      <c r="B47" t="s">
-        <v>113</v>
-      </c>
-      <c r="C47" t="s">
-        <v>114</v>
-      </c>
-      <c r="D47">
-        <v>76636</v>
-      </c>
-      <c r="E47">
-        <v>82885191</v>
-      </c>
-      <c r="F47">
-        <v>1081.54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>94</v>
-      </c>
-      <c r="B48" t="s">
-        <v>115</v>
-      </c>
-      <c r="C48" t="s">
-        <v>116</v>
-      </c>
-      <c r="D48">
+      <c r="D48" s="2">
         <v>76675</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="1">
         <v>83222757</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="1">
         <v>1085.4000000000001</v>
       </c>
     </row>
